--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MARYLAND_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MARYLAND_2016.xlsx
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C148">
@@ -4207,7 +4207,7 @@
         <v>22</v>
       </c>
       <c r="D214">
-        <v>0.009259259259259259</v>
+        <v>0.00925925925925926</v>
       </c>
     </row>
     <row r="215">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C399">
